--- a/info.xlsx
+++ b/info.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1碑影迷踪" sheetId="1" r:id="Re220554cce504984"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2消失的龙" sheetId="3" r:id="R11775461cccb408a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1隐秘的见证" sheetId="1" r:id="R921ed7b28deb42db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2消失的龙" sheetId="3" r:id="R92d348d292a24256"/>
   </x:sheets>
 </x:workbook>
 </file>
